--- a/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67761_completo.xlsx
+++ b/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67761_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R7b9a4702fdda4ff2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4de778d1906e455d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.8250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9292</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.4899</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.3743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.8250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67761_completo.xlsx
+++ b/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67761_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4de778d1906e455d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5ed3356d0353448f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,486 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.7982</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9292</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.1362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.6750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.6750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.6435</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.1362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.1362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.1362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.6346</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.6346</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.6346</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.6482</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.6482</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.6482</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.1635</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.6845</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.1635</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.1635</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1386</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.1635</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.6845</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -1389,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.9467</x:v>
+        <x:v>     62.9503</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.9467</x:v>
+        <x:v>     62.9503</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    536.2995</x:v>
+        <x:v>    103.4976</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    570.9655</x:v>
+        <x:v>    111.3896</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    586.3539</x:v>
+        <x:v>    131.1081</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    603.2335</x:v>
+        <x:v>    147.4612</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    328.1234</x:v>
+        <x:v>    155.4384</x:v>
       </x:c>
     </x:row>
     <x:row>
